--- a/Project_ETF/ETF_Investment_Portfolio/009819/ETF_Investment_Portfolio_20260617.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/009819/ETF_Investment_Portfolio_20260617.xlsx
@@ -611,12 +611,12 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>160,425</t>
+          <t>160,975</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>26.31%</t>
+          <t>27.10%</t>
         </is>
       </c>
     </row>
@@ -633,12 +633,12 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>116,360</t>
+          <t>116,810</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>9.54%</t>
+          <t>9.18%</t>
         </is>
       </c>
     </row>
@@ -655,12 +655,12 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>18,295</t>
+          <t>18,395</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>7.82%</t>
+          <t>8.26%</t>
         </is>
       </c>
     </row>
@@ -677,12 +677,12 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>59,235</t>
+          <t>59,485</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>7.19%</t>
+          <t>7.38%</t>
         </is>
       </c>
     </row>
@@ -699,12 +699,12 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>141,245</t>
+          <t>141,845</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>5.30%</t>
+          <t>5.21%</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>3.18%</t>
+          <t>3.11%</t>
         </is>
       </c>
     </row>
@@ -743,12 +743,12 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>76,205</t>
+          <t>76,525</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.13%</t>
+          <t>3.03%</t>
         </is>
       </c>
     </row>
@@ -765,12 +765,12 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>69,180</t>
+          <t>69,480</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.05%</t>
+          <t>2.84%</t>
         </is>
       </c>
     </row>
@@ -787,12 +787,12 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>52,555</t>
+          <t>52,775</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>2.88%</t>
+          <t>2.80%</t>
         </is>
       </c>
     </row>
@@ -809,144 +809,144 @@
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>22,985</t>
+          <t>23,085</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.68%</t>
+          <t>2.64%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>NET US</t>
+          <t>C_USD</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Cloudflare公司</t>
+          <t>CASH</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>21,263</t>
+          <t>4,918,877</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.14%</t>
+          <t>2.11%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>AEP US</t>
+          <t>NET US</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>美國電力公司</t>
+          <t>Cloudflare公司</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>36,690</t>
+          <t>21,363</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.07%</t>
+          <t>2.08%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>DLR US</t>
+          <t>AEP US</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>數位不動產信託公司</t>
+          <t>美國電力公司</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>23,595</t>
+          <t>36,840</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>1.96%</t>
+          <t>2.02%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>HPE US</t>
+          <t>DLR US</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>慧與</t>
+          <t>數位不動產信託公司</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>89,555</t>
+          <t>23,695</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>1.89%</t>
+          <t>1.90%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>D US</t>
+          <t>HPE US</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>道明尼能源公司</t>
+          <t>慧與</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>59,405</t>
+          <t>89,935</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1.77%</t>
+          <t>1.86%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>VST US</t>
+          <t>D US</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>維斯達能源公司</t>
+          <t>道明尼能源公司</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>22,690</t>
+          <t>59,655</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.57%</t>
+          <t>1.74%</t>
         </is>
       </c>
     </row>
@@ -963,34 +963,34 @@
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>13,631</t>
+          <t>13,731</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.57%</t>
+          <t>1.65%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>ETR US</t>
+          <t>VST US</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>安特吉公司</t>
+          <t>維斯達能源公司</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>30,928</t>
+          <t>22,790</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.51%</t>
+          <t>1.55%</t>
         </is>
       </c>
     </row>
@@ -1007,51 +1007,51 @@
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>9,310</t>
+          <t>9,410</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.47%</t>
+          <t>1.51%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>XEL US</t>
+          <t>ETR US</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Xcel 能源</t>
+          <t>安特吉公司</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>42,160</t>
+          <t>31,058</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.45%</t>
+          <t>1.47%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>EXC US</t>
+          <t>XEL US</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>愛克斯龍公司</t>
+          <t>Xcel 能源</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>69,158</t>
+          <t>42,340</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
@@ -1063,22 +1063,22 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>ED US</t>
+          <t>EXC US</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>聯合愛迪生</t>
+          <t>愛克斯龍公司</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>24,848</t>
+          <t>69,448</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>1.17%</t>
+          <t>1.36%</t>
         </is>
       </c>
     </row>
@@ -1095,12 +1095,12 @@
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>11,206</t>
+          <t>11,306</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.17%</t>
+          <t>1.21%</t>
         </is>
       </c>
     </row>
@@ -1117,188 +1117,188 @@
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>22,957</t>
+          <t>23,057</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.17%</t>
+          <t>1.14%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>WEC US</t>
+          <t>ED US</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>WEC能源集團公司</t>
+          <t>聯合愛迪生</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>21,535</t>
+          <t>24,948</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.08%</t>
+          <t>1.14%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>PCG US</t>
+          <t>C_NTD</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>太平洋電力瓦斯公司</t>
+          <t>CASH</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>147,645</t>
+          <t>84,003,340</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.08%</t>
+          <t>1.14%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>AEE US</t>
+          <t>WEC US</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>阿莫林公司</t>
+          <t>WEC能源集團公司</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>18,591</t>
+          <t>21,635</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>0.89%</t>
+          <t>1.04%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>CNP US</t>
+          <t>PCG US</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>Centerpoint能源</t>
+          <t>太平洋電力瓦斯公司</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>43,670</t>
+          <t>148,265</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>0.82%</t>
+          <t>1.04%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>PPL US</t>
+          <t>AEE US</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>PPL Corp</t>
+          <t>阿莫林公司</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>50,300</t>
+          <t>18,691</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.80%</t>
+          <t>0.87%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>NRG US</t>
+          <t>CNP US</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>NRG Energy Inc</t>
+          <t>Centerpoint能源</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>13,765</t>
+          <t>43,850</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.79%</t>
+          <t>0.80%</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>C_NTD</t>
+          <t>NRG US</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>CASH</t>
+          <t>NRG Energy Inc</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>49,473,340</t>
+          <t>13,865</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.68%</t>
+          <t>0.78%</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>C_USD</t>
+          <t>PPL US</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>CASH</t>
+          <t>PPL Corp</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>1,399,555</t>
+          <t>50,510</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.61%</t>
+          <t>0.76%</t>
         </is>
       </c>
     </row>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>3,481,767</t>
+          <t>-971,793</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
